--- a/output/yearly_benthic_cover_iteration_60_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_60_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.86846522280055</v>
+        <v>45.07802115452281</v>
       </c>
       <c r="M2" t="n">
-        <v>98.61586707363358</v>
+        <v>100.5192327804746</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.93714969942363</v>
+        <v>87.98557931367414</v>
       </c>
       <c r="C3" t="n">
-        <v>45.83766837987343</v>
+        <v>45.91164790995003</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228568210968342</v>
+        <v>2.228636448921134</v>
       </c>
       <c r="E3" t="n">
-        <v>5.649628555785914</v>
+        <v>5.694324162834435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428560703227808</v>
+        <v>0.7428788163070448</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94243491971241</v>
+        <v>33.96764888949924</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17137923484791</v>
+        <v>34.17242555012405</v>
       </c>
       <c r="I3" t="n">
-        <v>6.55943226826889</v>
+        <v>6.536672844069204</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64285043951738</v>
+        <v>4.64299260191903</v>
       </c>
       <c r="K3" t="n">
-        <v>12.06285030057636</v>
+        <v>12.01442068632586</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86401418020988</v>
+        <v>48.83928845521688</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7645328606597</v>
+        <v>106.7653570514928</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.0286670978271</v>
+        <v>86.96792277023499</v>
       </c>
       <c r="C4" t="n">
-        <v>42.5660374146747</v>
+        <v>42.52370300246566</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184730362614098</v>
+        <v>2.179045236024065</v>
       </c>
       <c r="E4" t="n">
-        <v>6.451439148096397</v>
+        <v>6.477385772226974</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444146044050736</v>
+        <v>0.7444330660593078</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27475810934563</v>
+        <v>33.21180694474979</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24307180263338</v>
+        <v>34.24392103872815</v>
       </c>
       <c r="I4" t="n">
-        <v>5.477661793200801</v>
+        <v>5.458624049576033</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65259127753171</v>
+        <v>4.652706662870674</v>
       </c>
       <c r="K4" t="n">
-        <v>12.9713329021729</v>
+        <v>13.032077229765</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28042323125604</v>
+        <v>44.26264552210075</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81779354810364</v>
+        <v>99.81842575433141</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.8035660419937</v>
+        <v>85.69580332422602</v>
       </c>
       <c r="C5" t="n">
-        <v>42.19102752879461</v>
+        <v>42.09869380215893</v>
       </c>
       <c r="D5" t="n">
-        <v>2.124636028893705</v>
+        <v>2.116582429544217</v>
       </c>
       <c r="E5" t="n">
-        <v>7.036120370747107</v>
+        <v>7.051196146296974</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457370356072534</v>
+        <v>0.7457525858160322</v>
       </c>
       <c r="G5" t="n">
-        <v>32.35948524432454</v>
+        <v>32.25978326220287</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30390363793365</v>
+        <v>34.30461894753748</v>
       </c>
       <c r="I5" t="n">
-        <v>4.572827251942118</v>
+        <v>4.55691629147824</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660856472545333</v>
+        <v>4.660953661350201</v>
       </c>
       <c r="K5" t="n">
-        <v>14.19643395800627</v>
+        <v>14.30419667577398</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46038124116576</v>
+        <v>43.44548107624553</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84784272796665</v>
+        <v>99.84837155417844</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.48328372252264</v>
+        <v>84.15036674996047</v>
       </c>
       <c r="C6" t="n">
-        <v>41.58081125620458</v>
+        <v>41.26078289007762</v>
       </c>
       <c r="D6" t="n">
-        <v>2.060173271394729</v>
+        <v>2.040693934290888</v>
       </c>
       <c r="E6" t="n">
-        <v>7.45871141925238</v>
+        <v>7.432239237021756</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468599604399015</v>
+        <v>0.7468760547631856</v>
       </c>
       <c r="G6" t="n">
-        <v>31.37767865640617</v>
+        <v>31.10313262823994</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35555818023547</v>
+        <v>34.35629851910654</v>
       </c>
       <c r="I6" t="n">
-        <v>3.816427482044601</v>
+        <v>3.803151034268247</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667874752749385</v>
+        <v>4.66797534226991</v>
       </c>
       <c r="K6" t="n">
-        <v>15.51671627747738</v>
+        <v>15.84963325003953</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77544948709742</v>
+        <v>42.76300285178621</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87297702077936</v>
+        <v>99.87341899190336</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.92649856868967</v>
+        <v>82.439759493091</v>
       </c>
       <c r="C7" t="n">
-        <v>40.6166975261664</v>
+        <v>40.14055001887246</v>
       </c>
       <c r="D7" t="n">
-        <v>1.984286560119625</v>
+        <v>1.957170316672367</v>
       </c>
       <c r="E7" t="n">
-        <v>7.714706814758721</v>
+        <v>7.656938090644535</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478159560824834</v>
+        <v>0.7478343730575387</v>
       </c>
       <c r="G7" t="n">
-        <v>30.22187837798122</v>
+        <v>29.83011166574957</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39953397979423</v>
+        <v>34.40038116064678</v>
       </c>
       <c r="I7" t="n">
-        <v>3.184427154437858</v>
+        <v>3.17335905471058</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673849725515522</v>
+        <v>4.673964831609617</v>
       </c>
       <c r="K7" t="n">
-        <v>17.07350143131034</v>
+        <v>17.560240506909</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20378916802202</v>
+        <v>42.19356638993332</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89398812549877</v>
+        <v>99.89435691571478</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.66033032666176</v>
+        <v>87.44067428815798</v>
       </c>
       <c r="C8" t="n">
-        <v>42.89039132604486</v>
+        <v>42.49416457311744</v>
       </c>
       <c r="D8" t="n">
-        <v>1.988454901369739</v>
+        <v>1.961419382178397</v>
       </c>
       <c r="E8" t="n">
-        <v>9.522069816372616</v>
+        <v>9.528026673938941</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493868743963403</v>
+        <v>0.7494579401082514</v>
       </c>
       <c r="G8" t="n">
-        <v>30.7205785084436</v>
+        <v>30.34751646661032</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47179622223165</v>
+        <v>34.47506524497956</v>
       </c>
       <c r="I8" t="n">
-        <v>5.524376038870685</v>
+        <v>5.695076454665943</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683667964977128</v>
+        <v>4.684112125676571</v>
       </c>
       <c r="K8" t="n">
-        <v>12.33966967333823</v>
+        <v>12.55932571184203</v>
       </c>
       <c r="L8" t="n">
-        <v>44.5861791523812</v>
+        <v>44.75708507882167</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81624015176429</v>
+        <v>99.81057536378114</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.50605299808618</v>
+        <v>85.30669369389435</v>
       </c>
       <c r="C9" t="n">
-        <v>41.59348722184985</v>
+        <v>41.24342270949812</v>
       </c>
       <c r="D9" t="n">
-        <v>1.890413241835014</v>
+        <v>1.864831366789633</v>
       </c>
       <c r="E9" t="n">
-        <v>9.821233826838018</v>
+        <v>9.851281514860805</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507341922625025</v>
+        <v>0.7508503507570171</v>
       </c>
       <c r="G9" t="n">
-        <v>29.2058866254344</v>
+        <v>28.85308523271873</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53377284407511</v>
+        <v>34.53911613482278</v>
       </c>
       <c r="I9" t="n">
-        <v>4.611923566000478</v>
+        <v>4.754714401714022</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692088701640642</v>
+        <v>4.692814692231357</v>
       </c>
       <c r="K9" t="n">
-        <v>14.49394700191383</v>
+        <v>14.69330630610564</v>
       </c>
       <c r="L9" t="n">
-        <v>43.75911088626768</v>
+        <v>43.90507441621109</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84654511003137</v>
+        <v>99.84180343181485</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.13333340136714</v>
+        <v>83.07503756898761</v>
       </c>
       <c r="C10" t="n">
-        <v>39.9360932293732</v>
+        <v>39.7487693404575</v>
       </c>
       <c r="D10" t="n">
-        <v>1.783540699407734</v>
+        <v>1.7650556857772</v>
       </c>
       <c r="E10" t="n">
-        <v>9.907534155125688</v>
+        <v>9.985628464260403</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7518928638794483</v>
+        <v>0.7520459779429638</v>
       </c>
       <c r="G10" t="n">
-        <v>27.55476226361325</v>
+        <v>27.30933372806644</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58707173845462</v>
+        <v>34.59411498537633</v>
       </c>
       <c r="I10" t="n">
-        <v>3.849201281639848</v>
+        <v>3.968571365420757</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699330399246553</v>
+        <v>4.700287362143523</v>
       </c>
       <c r="K10" t="n">
-        <v>16.86666659863285</v>
+        <v>16.92496243101238</v>
       </c>
       <c r="L10" t="n">
-        <v>43.06913118404948</v>
+        <v>43.19419282848249</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87189101205553</v>
+        <v>99.86792459995237</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.63751632914608</v>
+        <v>80.7727427898722</v>
       </c>
       <c r="C11" t="n">
-        <v>38.03652419892172</v>
+        <v>38.06095954435112</v>
       </c>
       <c r="D11" t="n">
-        <v>1.672334877657146</v>
+        <v>1.663288951209148</v>
       </c>
       <c r="E11" t="n">
-        <v>9.825109066452217</v>
+        <v>9.961836956679994</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7528911687296029</v>
+        <v>0.753073767932039</v>
       </c>
       <c r="G11" t="n">
-        <v>25.83669102381214</v>
+        <v>25.73477620043199</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63299376156174</v>
+        <v>34.64139332487379</v>
       </c>
       <c r="I11" t="n">
-        <v>3.211926626373234</v>
+        <v>3.311662539169987</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705569804560019</v>
+        <v>4.706711049575243</v>
       </c>
       <c r="K11" t="n">
-        <v>19.3624836708539</v>
+        <v>19.22725721012782</v>
       </c>
       <c r="L11" t="n">
-        <v>42.49406987240105</v>
+        <v>42.60154515203715</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89307774217667</v>
+        <v>99.88976190651609</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.92434575319191</v>
+        <v>78.40188323160541</v>
       </c>
       <c r="C12" t="n">
-        <v>35.81995648102652</v>
+        <v>36.20206944842668</v>
       </c>
       <c r="D12" t="n">
-        <v>1.552579508006393</v>
+        <v>1.559566499896726</v>
       </c>
       <c r="E12" t="n">
-        <v>9.568148398599748</v>
+        <v>9.801111724860929</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537541863988686</v>
+        <v>0.7539584036414956</v>
       </c>
       <c r="G12" t="n">
-        <v>23.98653378231301</v>
+        <v>24.1299593888101</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67269257434796</v>
+        <v>34.6820865675088</v>
       </c>
       <c r="I12" t="n">
-        <v>2.679673638532998</v>
+        <v>2.762960624128032</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71096366499293</v>
+        <v>4.712240022759347</v>
       </c>
       <c r="K12" t="n">
-        <v>22.07565424680809</v>
+        <v>21.59811676839458</v>
       </c>
       <c r="L12" t="n">
-        <v>42.01516908809945</v>
+        <v>42.10782315709069</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91077981593406</v>
+        <v>99.90800937391194</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.20842653707059</v>
+        <v>76.06367717094551</v>
       </c>
       <c r="C13" t="n">
-        <v>33.51727355343737</v>
+        <v>34.29013448767824</v>
       </c>
       <c r="D13" t="n">
-        <v>1.433890160161456</v>
+        <v>1.4582900452288</v>
       </c>
       <c r="E13" t="n">
-        <v>9.209242068909006</v>
+        <v>9.548770926579744</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545009320137106</v>
+        <v>0.7547199225519273</v>
       </c>
       <c r="G13" t="n">
-        <v>22.1528460149542</v>
+        <v>22.56298758072012</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70704287263069</v>
+        <v>34.71711643738866</v>
       </c>
       <c r="I13" t="n">
-        <v>2.235273663315817</v>
+        <v>2.304792742526712</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715630825085692</v>
+        <v>4.716999515949546</v>
       </c>
       <c r="K13" t="n">
-        <v>24.79157346292944</v>
+        <v>23.93632282905449</v>
       </c>
       <c r="L13" t="n">
-        <v>41.61671760478505</v>
+        <v>41.69679377704151</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92556462115185</v>
+        <v>99.92325109377424</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.58014362520179</v>
+        <v>82.94977163585071</v>
       </c>
       <c r="C14" t="n">
-        <v>38.13301794248466</v>
+        <v>38.61355024777311</v>
       </c>
       <c r="D14" t="n">
-        <v>1.435557287148156</v>
+        <v>1.459993144927726</v>
       </c>
       <c r="E14" t="n">
-        <v>11.75391424971431</v>
+        <v>11.94900525732944</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7553781602004974</v>
+        <v>0.7556013406738417</v>
       </c>
       <c r="G14" t="n">
-        <v>24.2325039867933</v>
+        <v>24.49404628398193</v>
       </c>
       <c r="H14" t="n">
-        <v>36.80129710920419</v>
+        <v>36.66236963732432</v>
       </c>
       <c r="I14" t="n">
-        <v>2.880379330888233</v>
+        <v>2.906247592401945</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72111350125311</v>
+        <v>4.722508379211511</v>
       </c>
       <c r="K14" t="n">
-        <v>17.41985637479821</v>
+        <v>17.05022836414929</v>
       </c>
       <c r="L14" t="n">
-        <v>44.35122453879512</v>
+        <v>44.23945947409889</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90409885607799</v>
+        <v>99.90323808602128</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.52367510318477</v>
+        <v>82.2160526716048</v>
       </c>
       <c r="C15" t="n">
-        <v>37.52093784668482</v>
+        <v>38.32857256161176</v>
       </c>
       <c r="D15" t="n">
-        <v>1.396400216464019</v>
+        <v>1.433138131024843</v>
       </c>
       <c r="E15" t="n">
-        <v>11.83375354960245</v>
+        <v>12.13325830679847</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561202463103783</v>
+        <v>0.7563440055028001</v>
       </c>
       <c r="G15" t="n">
-        <v>23.5715245330583</v>
+        <v>24.04350447439914</v>
       </c>
       <c r="H15" t="n">
-        <v>36.83745083041197</v>
+        <v>36.69840431726762</v>
       </c>
       <c r="I15" t="n">
-        <v>2.402674187897774</v>
+        <v>2.424253402219439</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725751539439866</v>
+        <v>4.7271500343925</v>
       </c>
       <c r="K15" t="n">
-        <v>18.47632489681525</v>
+        <v>17.78394732839519</v>
       </c>
       <c r="L15" t="n">
-        <v>43.92272671953082</v>
+        <v>43.80675101020412</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91998946303087</v>
+        <v>99.91927090021107</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.76284347921003</v>
+        <v>79.73767967961896</v>
       </c>
       <c r="C16" t="n">
-        <v>35.13067166977957</v>
+        <v>36.22457378715875</v>
       </c>
       <c r="D16" t="n">
-        <v>1.292738844089353</v>
+        <v>1.33983039967361</v>
       </c>
       <c r="E16" t="n">
-        <v>11.28926598326321</v>
+        <v>11.68028126652275</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567615002184717</v>
+        <v>0.7569832959507642</v>
       </c>
       <c r="G16" t="n">
-        <v>21.82169912251282</v>
+        <v>22.47809719950157</v>
       </c>
       <c r="H16" t="n">
-        <v>36.86869210377354</v>
+        <v>36.72942319117271</v>
       </c>
       <c r="I16" t="n">
-        <v>2.003926548987186</v>
+        <v>2.021918727105289</v>
       </c>
       <c r="J16" t="n">
-        <v>4.72975937636545</v>
+        <v>4.731145599692276</v>
       </c>
       <c r="K16" t="n">
-        <v>21.23715652078996</v>
+        <v>20.26232032038105</v>
       </c>
       <c r="L16" t="n">
-        <v>43.56543085976665</v>
+        <v>43.44576552017632</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93325905033618</v>
+        <v>99.93265962771612</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.4684926706603</v>
+        <v>81.46411246996811</v>
       </c>
       <c r="C17" t="n">
-        <v>36.37567696103505</v>
+        <v>37.48817285364387</v>
       </c>
       <c r="D17" t="n">
-        <v>1.293803266049942</v>
+        <v>1.340927109186295</v>
       </c>
       <c r="E17" t="n">
-        <v>12.07230884996453</v>
+        <v>12.47354186208407</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573846063960602</v>
+        <v>0.7576029197343529</v>
       </c>
       <c r="G17" t="n">
-        <v>22.28213143067359</v>
+        <v>22.94678666419646</v>
       </c>
       <c r="H17" t="n">
-        <v>37.34151388243202</v>
+        <v>37.20977798663427</v>
       </c>
       <c r="I17" t="n">
-        <v>1.987696845168765</v>
+        <v>2.000457679792967</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733653789975378</v>
+        <v>4.735018248339705</v>
       </c>
       <c r="K17" t="n">
-        <v>19.53150732933972</v>
+        <v>18.5358875300319</v>
       </c>
       <c r="L17" t="n">
-        <v>44.02661365790554</v>
+        <v>43.90931223107995</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93379794828033</v>
+        <v>99.93337261475573</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.86727358844203</v>
+        <v>78.9717397557197</v>
       </c>
       <c r="C18" t="n">
-        <v>34.0804780771393</v>
+        <v>35.30432718536844</v>
       </c>
       <c r="D18" t="n">
-        <v>1.200246714395395</v>
+        <v>1.250893913891496</v>
       </c>
       <c r="E18" t="n">
-        <v>11.47560981688635</v>
+        <v>11.91407409121017</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579220305851291</v>
+        <v>0.7581363805188445</v>
       </c>
       <c r="G18" t="n">
-        <v>20.6708823058111</v>
+        <v>21.40608209422222</v>
       </c>
       <c r="H18" t="n">
-        <v>37.36801063539927</v>
+        <v>37.23597899093144</v>
       </c>
       <c r="I18" t="n">
-        <v>1.657589394207729</v>
+        <v>1.668221906702739</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737012691157059</v>
+        <v>4.738352378242778</v>
       </c>
       <c r="K18" t="n">
-        <v>22.13272641155799</v>
+        <v>21.02826024428032</v>
       </c>
       <c r="L18" t="n">
-        <v>43.73158171004803</v>
+        <v>43.61184430146812</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94478619874532</v>
+        <v>99.94443173111688</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.81773620521697</v>
+        <v>77.96224786135085</v>
       </c>
       <c r="C19" t="n">
-        <v>33.28198802003839</v>
+        <v>34.54937158119907</v>
       </c>
       <c r="D19" t="n">
-        <v>1.163029261674008</v>
+        <v>1.215005483839442</v>
       </c>
       <c r="E19" t="n">
-        <v>11.35067297073416</v>
+        <v>11.80441816370299</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583776670356256</v>
+        <v>0.7585879070705928</v>
       </c>
       <c r="G19" t="n">
-        <v>20.02991609803155</v>
+        <v>20.79193674472804</v>
       </c>
       <c r="H19" t="n">
-        <v>37.39047498798562</v>
+        <v>37.25815578342786</v>
       </c>
       <c r="I19" t="n">
-        <v>1.385404800783328</v>
+        <v>1.392969359390707</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739860418972662</v>
+        <v>4.741174419191205</v>
       </c>
       <c r="K19" t="n">
-        <v>23.18226379478304</v>
+        <v>22.03775213864915</v>
       </c>
       <c r="L19" t="n">
-        <v>43.48959577038431</v>
+        <v>43.36647160560413</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95384758520575</v>
+        <v>99.95359532545235</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.0644542210879</v>
+        <v>75.24587959090147</v>
       </c>
       <c r="C20" t="n">
-        <v>30.74113134678842</v>
+        <v>32.04704799547375</v>
       </c>
       <c r="D20" t="n">
-        <v>1.065187167965394</v>
+        <v>1.117968143480644</v>
       </c>
       <c r="E20" t="n">
-        <v>10.58829294338442</v>
+        <v>11.05521680151217</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587719205846056</v>
+        <v>0.7589781954663303</v>
       </c>
       <c r="G20" t="n">
-        <v>18.34486053458125</v>
+        <v>19.1313728464968</v>
       </c>
       <c r="H20" t="n">
-        <v>37.40991296473892</v>
+        <v>37.27732485495314</v>
       </c>
       <c r="I20" t="n">
-        <v>1.155104186179529</v>
+        <v>1.161405027327818</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742324503653787</v>
+        <v>4.743613721664564</v>
       </c>
       <c r="K20" t="n">
-        <v>25.93554577891209</v>
+        <v>24.75412040909852</v>
       </c>
       <c r="L20" t="n">
-        <v>43.28483940761105</v>
+        <v>43.16013800211132</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96151653331157</v>
+        <v>99.96130640668359</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.57359857987694</v>
+        <v>81.12592002080916</v>
       </c>
       <c r="C21" t="n">
-        <v>34.82515672974432</v>
+        <v>35.73859717760562</v>
       </c>
       <c r="D21" t="n">
-        <v>1.06591229745098</v>
+        <v>1.118707881812026</v>
       </c>
       <c r="E21" t="n">
-        <v>12.76803452641029</v>
+        <v>13.03547699261903</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592884569352086</v>
+        <v>0.7594803969531466</v>
       </c>
       <c r="G21" t="n">
-        <v>20.25562878296792</v>
+        <v>20.84857945861032</v>
       </c>
       <c r="H21" t="n">
-        <v>39.33365980700759</v>
+        <v>39.00653829958542</v>
       </c>
       <c r="I21" t="n">
-        <v>1.64552185325988</v>
+        <v>1.61038451027206</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745552855845055</v>
+        <v>4.746752480957166</v>
       </c>
       <c r="K21" t="n">
-        <v>19.42640142012306</v>
+        <v>18.87407997919085</v>
       </c>
       <c r="L21" t="n">
-        <v>45.69362843609312</v>
+        <v>45.33367885473822</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9451865859605</v>
+        <v>99.94635601153468</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_60_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_60_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.07802115452281</v>
+        <v>45.06672048397532</v>
       </c>
       <c r="M2" t="n">
-        <v>100.5192327804746</v>
+        <v>100.2580939246127</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98557931367414</v>
+        <v>87.90970003361289</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91164790995003</v>
+        <v>45.87108073127207</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228636448921134</v>
+        <v>2.228472293796728</v>
       </c>
       <c r="E3" t="n">
-        <v>5.694324162834435</v>
+        <v>5.667030022088717</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428788163070448</v>
+        <v>0.7428240979322428</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96764888949924</v>
+        <v>33.95435379291263</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17242555012405</v>
+        <v>34.16990850488316</v>
       </c>
       <c r="I3" t="n">
-        <v>6.536672844069204</v>
+        <v>6.504460709922881</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64299260191903</v>
+        <v>4.642650612076517</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01442068632586</v>
+        <v>12.0902999663871</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83928845521688</v>
+        <v>48.80511545387822</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7653570514928</v>
+        <v>106.7664961515374</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.96792277023499</v>
+        <v>86.91185911660138</v>
       </c>
       <c r="C4" t="n">
-        <v>42.52370300246566</v>
+        <v>42.49823661054143</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179045236024065</v>
+        <v>2.179869731985694</v>
       </c>
       <c r="E4" t="n">
-        <v>6.477385772226974</v>
+        <v>6.448712451890724</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444330660593078</v>
+        <v>0.7443715582633572</v>
       </c>
       <c r="G4" t="n">
-        <v>33.21180694474979</v>
+        <v>33.21381571955739</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24392103872815</v>
+        <v>34.24109168011442</v>
       </c>
       <c r="I4" t="n">
-        <v>5.458624049576033</v>
+        <v>5.43167573564381</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652706662870674</v>
+        <v>4.652322239145982</v>
       </c>
       <c r="K4" t="n">
-        <v>13.032077229765</v>
+        <v>13.08814088339861</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26264552210075</v>
+        <v>44.23294304189541</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81842575433141</v>
+        <v>99.81932053583546</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.69580332422602</v>
+        <v>85.55315156345212</v>
       </c>
       <c r="C5" t="n">
-        <v>42.09869380215893</v>
+        <v>41.98246131627619</v>
       </c>
       <c r="D5" t="n">
-        <v>2.116582429544217</v>
+        <v>2.112811051753806</v>
       </c>
       <c r="E5" t="n">
-        <v>7.051196146296974</v>
+        <v>7.006064842938979</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457525858160322</v>
+        <v>0.7456866367773699</v>
       </c>
       <c r="G5" t="n">
-        <v>32.25978326220287</v>
+        <v>32.19206904592026</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30461894753748</v>
+        <v>34.301585291759</v>
       </c>
       <c r="I5" t="n">
-        <v>4.55691629147824</v>
+        <v>4.534393214444124</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660953661350201</v>
+        <v>4.660541479858561</v>
       </c>
       <c r="K5" t="n">
-        <v>14.30419667577398</v>
+        <v>14.4468484365479</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44548107624553</v>
+        <v>43.41981036563025</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84837155417844</v>
+        <v>99.84912011845432</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.15036674996047</v>
+        <v>84.03606928603041</v>
       </c>
       <c r="C6" t="n">
-        <v>41.26078289007762</v>
+        <v>41.16932613530819</v>
       </c>
       <c r="D6" t="n">
-        <v>2.040693934290888</v>
+        <v>2.038276265346509</v>
       </c>
       <c r="E6" t="n">
-        <v>7.432239237021756</v>
+        <v>7.38963025453326</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468760547631856</v>
+        <v>0.7468059682818369</v>
       </c>
       <c r="G6" t="n">
-        <v>31.10313262823994</v>
+        <v>31.05641188985089</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35629851910654</v>
+        <v>34.35307454096449</v>
       </c>
       <c r="I6" t="n">
-        <v>3.803151034268247</v>
+        <v>3.784333065291946</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66797534226991</v>
+        <v>4.66753730176148</v>
       </c>
       <c r="K6" t="n">
-        <v>15.84963325003953</v>
+        <v>15.96393071396959</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76300285178621</v>
+        <v>42.74078778365433</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87341899190336</v>
+        <v>99.87404463293211</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.439759493091</v>
+        <v>82.20377680009369</v>
       </c>
       <c r="C7" t="n">
-        <v>40.14055001887246</v>
+        <v>39.92443370669966</v>
       </c>
       <c r="D7" t="n">
-        <v>1.957170316672367</v>
+        <v>1.948516999720867</v>
       </c>
       <c r="E7" t="n">
-        <v>7.656938090644535</v>
+        <v>7.590489020526864</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478343730575387</v>
+        <v>0.7477621899525321</v>
       </c>
       <c r="G7" t="n">
-        <v>29.83011166574957</v>
+        <v>29.68878534599445</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40038116064678</v>
+        <v>34.39706073781646</v>
       </c>
       <c r="I7" t="n">
-        <v>3.17335905471058</v>
+        <v>3.157648818879187</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673964831609617</v>
+        <v>4.673513687203325</v>
       </c>
       <c r="K7" t="n">
-        <v>17.560240506909</v>
+        <v>17.79622319990631</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19356638993332</v>
+        <v>42.17422273046925</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89435691571478</v>
+        <v>99.89487963707522</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.44067428815798</v>
+        <v>87.16276032335992</v>
       </c>
       <c r="C8" t="n">
-        <v>42.49416457311744</v>
+        <v>42.27729400336382</v>
       </c>
       <c r="D8" t="n">
-        <v>1.961419382178397</v>
+        <v>1.952719316607478</v>
       </c>
       <c r="E8" t="n">
-        <v>9.528026673938941</v>
+        <v>9.457965103806208</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494579401082514</v>
+        <v>0.7493748695845069</v>
       </c>
       <c r="G8" t="n">
-        <v>30.34751646661032</v>
+        <v>30.20841307441457</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47506524497956</v>
+        <v>34.4712440008873</v>
       </c>
       <c r="I8" t="n">
-        <v>5.695076454665943</v>
+        <v>5.639451023156679</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684112125676571</v>
+        <v>4.683592934903168</v>
       </c>
       <c r="K8" t="n">
-        <v>12.55932571184203</v>
+        <v>12.83723967664008</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75708507882167</v>
+        <v>44.69788916209363</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81057536378114</v>
+        <v>99.81242284209753</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.30669369389435</v>
+        <v>84.94297891369682</v>
       </c>
       <c r="C9" t="n">
-        <v>41.24342270949812</v>
+        <v>40.93194804129919</v>
       </c>
       <c r="D9" t="n">
-        <v>1.864831366789633</v>
+        <v>1.851985194172717</v>
       </c>
       <c r="E9" t="n">
-        <v>9.851281514860805</v>
+        <v>9.75476521031543</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508503507570171</v>
+        <v>0.7507594163491</v>
       </c>
       <c r="G9" t="n">
-        <v>28.85308523271873</v>
+        <v>28.65006418355368</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53911613482278</v>
+        <v>34.53493315205858</v>
       </c>
       <c r="I9" t="n">
-        <v>4.754714401714022</v>
+        <v>4.70822540506543</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692814692231357</v>
+        <v>4.692246352181875</v>
       </c>
       <c r="K9" t="n">
-        <v>14.69330630610564</v>
+        <v>15.0570210863032</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90507441621109</v>
+        <v>43.8543794550877</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84180343181485</v>
+        <v>99.84334858269008</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.07503756898761</v>
+        <v>82.55723068169075</v>
       </c>
       <c r="C10" t="n">
-        <v>39.7487693404575</v>
+        <v>39.27574596753286</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7650556857772</v>
+        <v>1.744994953571925</v>
       </c>
       <c r="E10" t="n">
-        <v>9.985628464260403</v>
+        <v>9.846184616733559</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520459779429638</v>
+        <v>0.7519506280634093</v>
       </c>
       <c r="G10" t="n">
-        <v>27.30933372806644</v>
+        <v>26.99493364046323</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59411498537633</v>
+        <v>34.58972889091681</v>
       </c>
       <c r="I10" t="n">
-        <v>3.968571365420757</v>
+        <v>3.929746526545507</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700287362143523</v>
+        <v>4.699691425396308</v>
       </c>
       <c r="K10" t="n">
-        <v>16.92496243101238</v>
+        <v>17.44276931830925</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19419282848249</v>
+        <v>43.15070067512832</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86792459995237</v>
+        <v>99.86921596097042</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.7727427898722</v>
+        <v>80.00857330396147</v>
       </c>
       <c r="C11" t="n">
-        <v>38.06095954435112</v>
+        <v>37.33520458978972</v>
       </c>
       <c r="D11" t="n">
-        <v>1.663288951209148</v>
+        <v>1.631962586619782</v>
       </c>
       <c r="E11" t="n">
-        <v>9.961836956679994</v>
+        <v>9.754940014392453</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753073767932039</v>
+        <v>0.7529779528628496</v>
       </c>
       <c r="G11" t="n">
-        <v>25.73477620043199</v>
+        <v>25.24633188155744</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64139332487379</v>
+        <v>34.63698583169106</v>
       </c>
       <c r="I11" t="n">
-        <v>3.311662539169987</v>
+        <v>3.279262831445062</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706711049575243</v>
+        <v>4.70611220539281</v>
       </c>
       <c r="K11" t="n">
-        <v>19.22725721012782</v>
+        <v>19.99142669603853</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60154515203715</v>
+        <v>42.56420908843437</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88976190651609</v>
+        <v>99.89084037426262</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.40188323160541</v>
+        <v>77.49007968901635</v>
       </c>
       <c r="C12" t="n">
-        <v>36.20206944842668</v>
+        <v>35.32317199152145</v>
       </c>
       <c r="D12" t="n">
-        <v>1.559566499896726</v>
+        <v>1.521555605822628</v>
       </c>
       <c r="E12" t="n">
-        <v>9.801111724860929</v>
+        <v>9.550979350378768</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539584036414956</v>
+        <v>0.7538641303195275</v>
       </c>
       <c r="G12" t="n">
-        <v>24.1299593888101</v>
+        <v>23.53834463840683</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6820865675088</v>
+        <v>34.67774999469825</v>
       </c>
       <c r="I12" t="n">
-        <v>2.762960624128032</v>
+        <v>2.735935154893311</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712240022759347</v>
+        <v>4.711650814497046</v>
       </c>
       <c r="K12" t="n">
-        <v>21.59811676839458</v>
+        <v>22.50992031098365</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10782315709069</v>
+        <v>42.07581706328809</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90800937391194</v>
+        <v>99.90890936579318</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.06367717094551</v>
+        <v>74.92670327942861</v>
       </c>
       <c r="C13" t="n">
-        <v>34.29013448767824</v>
+        <v>33.18135830907519</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4582900452288</v>
+        <v>1.410295499480596</v>
       </c>
       <c r="E13" t="n">
-        <v>9.548770926579744</v>
+        <v>9.232963690270418</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547199225519273</v>
+        <v>0.7546295515128553</v>
       </c>
       <c r="G13" t="n">
-        <v>22.56298758072012</v>
+        <v>21.81715961068736</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71711643738866</v>
+        <v>34.71295936959132</v>
       </c>
       <c r="I13" t="n">
-        <v>2.304792742526712</v>
+        <v>2.282260860930713</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716999515949546</v>
+        <v>4.716434696955345</v>
       </c>
       <c r="K13" t="n">
-        <v>23.93632282905449</v>
+        <v>25.07329672057138</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69679377704151</v>
+        <v>41.66934677160639</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92325109377424</v>
+        <v>99.92400180125296</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.94977163585071</v>
+        <v>82.4584167273522</v>
       </c>
       <c r="C14" t="n">
-        <v>38.61355024777311</v>
+        <v>37.74003906478047</v>
       </c>
       <c r="D14" t="n">
-        <v>1.459993144927726</v>
+        <v>1.412114064854084</v>
       </c>
       <c r="E14" t="n">
-        <v>11.94900525732944</v>
+        <v>11.7761061149433</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556013406738417</v>
+        <v>0.7556026406085071</v>
       </c>
       <c r="G14" t="n">
-        <v>24.49404628398193</v>
+        <v>23.84488173913262</v>
       </c>
       <c r="H14" t="n">
-        <v>36.66236963732432</v>
+        <v>36.7573105342305</v>
       </c>
       <c r="I14" t="n">
-        <v>2.906247592401945</v>
+        <v>3.189885129780031</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722508379211511</v>
+        <v>4.722516503803169</v>
       </c>
       <c r="K14" t="n">
-        <v>17.05022836414929</v>
+        <v>17.54158327264778</v>
       </c>
       <c r="L14" t="n">
-        <v>44.23945947409889</v>
+        <v>44.61218509276086</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90323808602128</v>
+        <v>99.8938074301891</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.2160526716048</v>
+        <v>81.56204180346673</v>
       </c>
       <c r="C15" t="n">
-        <v>38.32857256161176</v>
+        <v>37.31510596439568</v>
       </c>
       <c r="D15" t="n">
-        <v>1.433138131024843</v>
+        <v>1.377112367196669</v>
       </c>
       <c r="E15" t="n">
-        <v>12.13325830679847</v>
+        <v>11.94802163629145</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563440055028001</v>
+        <v>0.756424410053405</v>
       </c>
       <c r="G15" t="n">
-        <v>24.04350447439914</v>
+        <v>23.27413027551215</v>
       </c>
       <c r="H15" t="n">
-        <v>36.69840431726762</v>
+        <v>36.81757192859385</v>
       </c>
       <c r="I15" t="n">
-        <v>2.424253402219439</v>
+        <v>2.661128622985412</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7271500343925</v>
+        <v>4.72765256283378</v>
       </c>
       <c r="K15" t="n">
-        <v>17.78394732839519</v>
+        <v>18.43795819653328</v>
       </c>
       <c r="L15" t="n">
-        <v>43.80675101020412</v>
+        <v>44.15832791879934</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91927090021107</v>
+        <v>99.91139207972832</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.73767967961896</v>
+        <v>78.81672179321909</v>
       </c>
       <c r="C16" t="n">
-        <v>36.22457378715875</v>
+        <v>34.97996987644293</v>
       </c>
       <c r="D16" t="n">
-        <v>1.33983039967361</v>
+        <v>1.275010623186416</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68028126652275</v>
+        <v>11.43212062977518</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569832959507642</v>
+        <v>0.7571345076429269</v>
       </c>
       <c r="G16" t="n">
-        <v>22.47809719950157</v>
+        <v>21.54854175560872</v>
       </c>
       <c r="H16" t="n">
-        <v>36.72942319117271</v>
+        <v>36.85213462743206</v>
       </c>
       <c r="I16" t="n">
-        <v>2.021918727105289</v>
+        <v>2.219688976805482</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731145599692276</v>
+        <v>4.732090672768293</v>
       </c>
       <c r="K16" t="n">
-        <v>20.26232032038105</v>
+        <v>21.18327820678089</v>
       </c>
       <c r="L16" t="n">
-        <v>43.44576552017632</v>
+        <v>43.76283167724881</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93265962771612</v>
+        <v>99.92607976047265</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.46411246996811</v>
+        <v>80.82385588716649</v>
       </c>
       <c r="C17" t="n">
-        <v>37.48817285364387</v>
+        <v>36.4127471028794</v>
       </c>
       <c r="D17" t="n">
-        <v>1.340927109186295</v>
+        <v>1.276188989814634</v>
       </c>
       <c r="E17" t="n">
-        <v>12.47354186208407</v>
+        <v>12.33004672421536</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576029197343529</v>
+        <v>0.757834252429875</v>
       </c>
       <c r="G17" t="n">
-        <v>22.94678666419646</v>
+        <v>22.08232984899107</v>
       </c>
       <c r="H17" t="n">
-        <v>37.20977798663427</v>
+        <v>37.40006632307468</v>
       </c>
       <c r="I17" t="n">
-        <v>2.000457679792967</v>
+        <v>2.240925670954161</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735018248339705</v>
+        <v>4.736464077686719</v>
       </c>
       <c r="K17" t="n">
-        <v>18.5358875300319</v>
+        <v>19.1761441128335</v>
       </c>
       <c r="L17" t="n">
-        <v>43.90931223107995</v>
+        <v>44.33648023373432</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93337261475573</v>
+        <v>99.92537144944723</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.9717397557197</v>
+        <v>78.25439634318062</v>
       </c>
       <c r="C18" t="n">
-        <v>35.30432718536844</v>
+        <v>34.18817994798646</v>
       </c>
       <c r="D18" t="n">
-        <v>1.250893913891496</v>
+        <v>1.185250387295542</v>
       </c>
       <c r="E18" t="n">
-        <v>11.91407409121017</v>
+        <v>11.76292040648174</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581363805188445</v>
+        <v>0.7584375561947307</v>
       </c>
       <c r="G18" t="n">
-        <v>21.40608209422222</v>
+        <v>20.5087884433999</v>
       </c>
       <c r="H18" t="n">
-        <v>37.23597899093144</v>
+        <v>37.42984011694348</v>
       </c>
       <c r="I18" t="n">
-        <v>1.668221906702739</v>
+        <v>1.868924706648152</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738352378242778</v>
+        <v>4.740234726217067</v>
       </c>
       <c r="K18" t="n">
-        <v>21.02826024428032</v>
+        <v>21.74560365681938</v>
       </c>
       <c r="L18" t="n">
-        <v>43.61184430146812</v>
+        <v>44.00396845988987</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94443173111688</v>
+        <v>99.93775206469572</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.96224786135085</v>
+        <v>77.29869440552747</v>
       </c>
       <c r="C19" t="n">
-        <v>34.54937158119907</v>
+        <v>33.51926773164212</v>
       </c>
       <c r="D19" t="n">
-        <v>1.215005483839442</v>
+        <v>1.152167379044365</v>
       </c>
       <c r="E19" t="n">
-        <v>11.80441816370299</v>
+        <v>11.69433812513944</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585879070705928</v>
+        <v>0.7589472727631161</v>
       </c>
       <c r="G19" t="n">
-        <v>20.79193674472804</v>
+        <v>19.93634195903909</v>
       </c>
       <c r="H19" t="n">
-        <v>37.25815578342786</v>
+        <v>37.45499526584637</v>
       </c>
       <c r="I19" t="n">
-        <v>1.392969359390707</v>
+        <v>1.558483948925608</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741174419191205</v>
+        <v>4.743420454769476</v>
       </c>
       <c r="K19" t="n">
-        <v>22.03775213864915</v>
+        <v>22.70130559447253</v>
       </c>
       <c r="L19" t="n">
-        <v>43.36647160560413</v>
+        <v>43.72751209870068</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95359532545235</v>
+        <v>99.94808542481533</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.24587959090147</v>
+        <v>74.62592555062371</v>
       </c>
       <c r="C20" t="n">
-        <v>32.04704799547375</v>
+        <v>31.08548198509968</v>
       </c>
       <c r="D20" t="n">
-        <v>1.117968143480644</v>
+        <v>1.05884600632037</v>
       </c>
       <c r="E20" t="n">
-        <v>11.05521680151217</v>
+        <v>10.96372095913342</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589781954663303</v>
+        <v>0.7593878009672839</v>
       </c>
       <c r="G20" t="n">
-        <v>19.1313728464968</v>
+        <v>18.32157067445746</v>
       </c>
       <c r="H20" t="n">
-        <v>37.27732485495314</v>
+        <v>37.47673588261083</v>
       </c>
       <c r="I20" t="n">
-        <v>1.161405027327818</v>
+        <v>1.299490471088826</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743613721664564</v>
+        <v>4.746173756045524</v>
       </c>
       <c r="K20" t="n">
-        <v>24.75412040909852</v>
+        <v>25.3740744493763</v>
       </c>
       <c r="L20" t="n">
-        <v>43.16013800211132</v>
+        <v>43.49715234472052</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96130640668359</v>
+        <v>99.95670877919649</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.12592002080916</v>
+        <v>81.22429114077468</v>
       </c>
       <c r="C21" t="n">
-        <v>35.73859717760562</v>
+        <v>35.11925699526283</v>
       </c>
       <c r="D21" t="n">
-        <v>1.118707881812026</v>
+        <v>1.05970399849226</v>
       </c>
       <c r="E21" t="n">
-        <v>13.03547699261903</v>
+        <v>13.1466396086843</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594803969531466</v>
+        <v>0.7600031395384919</v>
       </c>
       <c r="G21" t="n">
-        <v>20.84857945861032</v>
+        <v>20.18136768938871</v>
       </c>
       <c r="H21" t="n">
-        <v>39.00653829958542</v>
+        <v>39.35205449530203</v>
       </c>
       <c r="I21" t="n">
-        <v>1.61038451027206</v>
+        <v>1.974502587253312</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746752480957166</v>
+        <v>4.750019622115573</v>
       </c>
       <c r="K21" t="n">
-        <v>18.87407997919085</v>
+        <v>18.77570885922531</v>
       </c>
       <c r="L21" t="n">
-        <v>45.33367885473822</v>
+        <v>46.03927068131314</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94635601153468</v>
+        <v>99.93423653580129</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_60_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_60_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.06672048397532</v>
+        <v>43.47586446532672</v>
       </c>
       <c r="M2" t="n">
-        <v>100.2580939246127</v>
+        <v>96.13312986403869</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.90970003361289</v>
+        <v>81.54636879633243</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87108073127207</v>
+        <v>43.30192435188799</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228472293796728</v>
+        <v>2.184217407176495</v>
       </c>
       <c r="E3" t="n">
-        <v>5.667030022088717</v>
+        <v>4.15264149058075</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428240979322428</v>
+        <v>0.7376819692126924</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95435379291263</v>
+        <v>32.85427016627978</v>
       </c>
       <c r="H3" t="n">
-        <v>34.16990850488316</v>
+        <v>33.93337058378384</v>
       </c>
       <c r="I3" t="n">
-        <v>6.504460709922881</v>
+        <v>3.073674871719551</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642650612076517</v>
+        <v>4.610512307579327</v>
       </c>
       <c r="K3" t="n">
-        <v>12.0902999663871</v>
+        <v>18.45363120366756</v>
       </c>
       <c r="L3" t="n">
-        <v>48.80511545387822</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7664961515374</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.91185911660138</v>
+        <v>88.59985594759104</v>
       </c>
       <c r="C4" t="n">
-        <v>42.49823661054143</v>
+        <v>42.84490129322624</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179869731985694</v>
+        <v>2.189967074185312</v>
       </c>
       <c r="E4" t="n">
-        <v>6.448712451890724</v>
+        <v>6.501463013536849</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443715582633572</v>
+        <v>0.7396238206362025</v>
       </c>
       <c r="G4" t="n">
-        <v>33.21381571955739</v>
+        <v>33.52663099086438</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24109168011442</v>
+        <v>34.02269574926531</v>
       </c>
       <c r="I4" t="n">
-        <v>5.43167573564381</v>
+        <v>6.996826420126725</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652322239145982</v>
+        <v>4.622648878976266</v>
       </c>
       <c r="K4" t="n">
-        <v>13.08814088339861</v>
+        <v>11.40014405240897</v>
       </c>
       <c r="L4" t="n">
-        <v>44.23294304189541</v>
+        <v>45.52233943620344</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81932053583546</v>
+        <v>99.76738478183864</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.55315156345212</v>
+        <v>87.44814704773077</v>
       </c>
       <c r="C5" t="n">
-        <v>41.98246131627619</v>
+        <v>42.7777574466023</v>
       </c>
       <c r="D5" t="n">
-        <v>2.112811051753806</v>
+        <v>2.134969800674659</v>
       </c>
       <c r="E5" t="n">
-        <v>7.006064842938979</v>
+        <v>7.312135974827012</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7456866367773699</v>
+        <v>0.741271319731851</v>
       </c>
       <c r="G5" t="n">
-        <v>32.19206904592026</v>
+        <v>32.68466705623251</v>
       </c>
       <c r="H5" t="n">
-        <v>34.301585291759</v>
+        <v>34.09848070766514</v>
       </c>
       <c r="I5" t="n">
-        <v>4.534393214444124</v>
+        <v>5.843676440275529</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660541479858561</v>
+        <v>4.632945748324069</v>
       </c>
       <c r="K5" t="n">
-        <v>14.4468484365479</v>
+        <v>12.55185295226923</v>
       </c>
       <c r="L5" t="n">
-        <v>43.41981036563025</v>
+        <v>44.47603331168051</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84912011845432</v>
+        <v>99.80564371055203</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.03606928603041</v>
+        <v>86.11646688693322</v>
       </c>
       <c r="C6" t="n">
-        <v>41.16932613530819</v>
+        <v>42.35298571848451</v>
       </c>
       <c r="D6" t="n">
-        <v>2.038276265346509</v>
+        <v>2.071393186257478</v>
       </c>
       <c r="E6" t="n">
-        <v>7.38963025453326</v>
+        <v>7.907544583167477</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468059682818369</v>
+        <v>0.7426712101653149</v>
       </c>
       <c r="G6" t="n">
-        <v>31.05641188985089</v>
+        <v>31.71136032649263</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35307454096449</v>
+        <v>34.16287566760448</v>
       </c>
       <c r="I6" t="n">
-        <v>3.784333065291946</v>
+        <v>4.878926849712624</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66753730176148</v>
+        <v>4.641695063533218</v>
       </c>
       <c r="K6" t="n">
-        <v>15.96393071396959</v>
+        <v>13.88353311306679</v>
       </c>
       <c r="L6" t="n">
-        <v>42.74078778365433</v>
+        <v>43.60115682288548</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87404463293211</v>
+        <v>99.83767565443678</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.20377680009369</v>
+        <v>84.50960346324784</v>
       </c>
       <c r="C7" t="n">
-        <v>39.92443370669966</v>
+        <v>41.50373461152429</v>
       </c>
       <c r="D7" t="n">
-        <v>1.948516999720867</v>
+        <v>1.994754697360866</v>
       </c>
       <c r="E7" t="n">
-        <v>7.590489020526864</v>
+        <v>8.293694280642191</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477621899525321</v>
+        <v>0.7438641247711224</v>
       </c>
       <c r="G7" t="n">
-        <v>29.68878534599445</v>
+        <v>30.53808682515927</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39706073781646</v>
+        <v>34.21774973947163</v>
       </c>
       <c r="I7" t="n">
-        <v>3.157648818879187</v>
+        <v>4.07230301602324</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673513687203325</v>
+        <v>4.649150779819515</v>
       </c>
       <c r="K7" t="n">
-        <v>17.79622319990631</v>
+        <v>15.49039653675215</v>
       </c>
       <c r="L7" t="n">
-        <v>42.17422273046925</v>
+        <v>42.87034310589822</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89487963707522</v>
+        <v>99.86447425417468</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.16276032335992</v>
+        <v>82.73604369817481</v>
       </c>
       <c r="C8" t="n">
-        <v>42.27729400336382</v>
+        <v>40.36243780397476</v>
       </c>
       <c r="D8" t="n">
-        <v>1.952719316607478</v>
+        <v>1.910712254287069</v>
       </c>
       <c r="E8" t="n">
-        <v>9.457965103806208</v>
+        <v>8.510638693331591</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493748695845069</v>
+        <v>0.744882553490529</v>
       </c>
       <c r="G8" t="n">
-        <v>30.20841307441457</v>
+        <v>29.25146475228901</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4712440008873</v>
+        <v>34.26459746056433</v>
       </c>
       <c r="I8" t="n">
-        <v>5.639451023156679</v>
+        <v>3.39823202489647</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683592934903168</v>
+        <v>4.655515959315807</v>
       </c>
       <c r="K8" t="n">
-        <v>12.83723967664008</v>
+        <v>17.26395630182519</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69788916209363</v>
+        <v>42.26048636597718</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81242284209753</v>
+        <v>99.88688047177713</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.94297891369682</v>
+        <v>80.93714016751443</v>
       </c>
       <c r="C9" t="n">
-        <v>40.93194804129919</v>
+        <v>39.09077139286233</v>
       </c>
       <c r="D9" t="n">
-        <v>1.851985194172717</v>
+        <v>1.826203775313847</v>
       </c>
       <c r="E9" t="n">
-        <v>9.75476521031543</v>
+        <v>8.606751265183675</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507594163491</v>
+        <v>0.7457523091821608</v>
       </c>
       <c r="G9" t="n">
-        <v>28.65006418355368</v>
+        <v>27.95770804538125</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53493315205858</v>
+        <v>34.3046062223794</v>
       </c>
       <c r="I9" t="n">
-        <v>4.70822540506543</v>
+        <v>2.835166617685606</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692246352181875</v>
+        <v>4.660951932388506</v>
       </c>
       <c r="K9" t="n">
-        <v>15.0570210863032</v>
+        <v>19.06285983248557</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8543794550877</v>
+        <v>41.7519734406272</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84334858269008</v>
+        <v>99.90560466597509</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.55723068169075</v>
+        <v>85.76199775214276</v>
       </c>
       <c r="C10" t="n">
-        <v>39.27574596753286</v>
+        <v>42.37726516233985</v>
       </c>
       <c r="D10" t="n">
-        <v>1.744994953571925</v>
+        <v>1.828297266312407</v>
       </c>
       <c r="E10" t="n">
-        <v>9.846184616733559</v>
+        <v>10.4846859806101</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519506280634093</v>
+        <v>0.746607211448563</v>
       </c>
       <c r="G10" t="n">
-        <v>26.99493364046323</v>
+        <v>29.36625439937857</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58972889091681</v>
+        <v>35.72042842060721</v>
       </c>
       <c r="I10" t="n">
-        <v>3.929746526545507</v>
+        <v>2.949429402232385</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699691425396308</v>
+        <v>4.666295071553519</v>
       </c>
       <c r="K10" t="n">
-        <v>17.44276931830925</v>
+        <v>14.23800224785726</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15070067512832</v>
+        <v>43.28653085115744</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86921596097042</v>
+        <v>99.90179826135454</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.00857330396147</v>
+        <v>85.53830653773012</v>
       </c>
       <c r="C11" t="n">
-        <v>37.33520458978972</v>
+        <v>42.54849815993027</v>
       </c>
       <c r="D11" t="n">
-        <v>1.631962586619782</v>
+        <v>1.815682270910031</v>
       </c>
       <c r="E11" t="n">
-        <v>9.754940014392453</v>
+        <v>10.84664713258106</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529779528628496</v>
+        <v>0.7473361358302821</v>
       </c>
       <c r="G11" t="n">
-        <v>25.24633188155744</v>
+        <v>29.180373389622</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63698583169106</v>
+        <v>35.77204487553294</v>
       </c>
       <c r="I11" t="n">
-        <v>3.279262831445062</v>
+        <v>2.505371884314528</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70611220539281</v>
+        <v>4.670850848939264</v>
       </c>
       <c r="K11" t="n">
-        <v>19.99142669603853</v>
+        <v>14.4616934622699</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56420908843437</v>
+        <v>42.9063774365982</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89084037426262</v>
+        <v>99.91656905879836</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.49007968901635</v>
+        <v>83.74933641862046</v>
       </c>
       <c r="C12" t="n">
-        <v>35.32317199152145</v>
+        <v>41.14903712709962</v>
       </c>
       <c r="D12" t="n">
-        <v>1.521555605822628</v>
+        <v>1.739498891949152</v>
       </c>
       <c r="E12" t="n">
-        <v>9.550979350378768</v>
+        <v>10.73979535539241</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538641303195275</v>
+        <v>0.7479576704790626</v>
       </c>
       <c r="G12" t="n">
-        <v>23.53834463840683</v>
+        <v>27.9560074970987</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67774999469825</v>
+        <v>35.80179529744071</v>
       </c>
       <c r="I12" t="n">
-        <v>2.735935154893311</v>
+        <v>2.089546265766272</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711650814497046</v>
+        <v>4.674735440494143</v>
       </c>
       <c r="K12" t="n">
-        <v>22.50992031098365</v>
+        <v>16.25066358137956</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07581706328809</v>
+        <v>42.53070562806765</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90890936579318</v>
+        <v>99.93040633654682</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.92670327942861</v>
+        <v>84.93017273981148</v>
       </c>
       <c r="C13" t="n">
-        <v>33.18135830907519</v>
+        <v>42.13393430648544</v>
       </c>
       <c r="D13" t="n">
-        <v>1.410295499480596</v>
+        <v>1.740825358934957</v>
       </c>
       <c r="E13" t="n">
-        <v>9.232963690270418</v>
+        <v>11.38559521444261</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546295515128553</v>
+        <v>0.7485280308059714</v>
       </c>
       <c r="G13" t="n">
-        <v>21.81715961068736</v>
+        <v>28.29111522713131</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71295936959132</v>
+        <v>36.1428858875619</v>
       </c>
       <c r="I13" t="n">
-        <v>2.282260860930713</v>
+        <v>1.942922828397411</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716434696955345</v>
+        <v>4.678300192537323</v>
       </c>
       <c r="K13" t="n">
-        <v>25.07329672057138</v>
+        <v>15.06982726018854</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66934677160639</v>
+        <v>42.73152368772574</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92400180125296</v>
+        <v>99.9352852543997</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.4584167273522</v>
+        <v>83.13122806402666</v>
       </c>
       <c r="C14" t="n">
-        <v>37.74003906478047</v>
+        <v>40.636969548363</v>
       </c>
       <c r="D14" t="n">
-        <v>1.412114064854084</v>
+        <v>1.66629548672316</v>
       </c>
       <c r="E14" t="n">
-        <v>11.7761061149433</v>
+        <v>11.16816997282336</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556026406085071</v>
+        <v>0.7490143024717858</v>
       </c>
       <c r="G14" t="n">
-        <v>23.84488173913262</v>
+        <v>27.07988907409703</v>
       </c>
       <c r="H14" t="n">
-        <v>36.7573105342305</v>
+        <v>36.16636565131766</v>
       </c>
       <c r="I14" t="n">
-        <v>3.189885129780031</v>
+        <v>1.620154186144993</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722516503803169</v>
+        <v>4.681339390448663</v>
       </c>
       <c r="K14" t="n">
-        <v>17.54158327264778</v>
+        <v>16.86877193597335</v>
       </c>
       <c r="L14" t="n">
-        <v>44.61218509276086</v>
+        <v>42.44028843709707</v>
       </c>
       <c r="M14" t="n">
-        <v>99.8938074301891</v>
+        <v>99.94602992143342</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.56204180346673</v>
+        <v>82.32538009594974</v>
       </c>
       <c r="C15" t="n">
-        <v>37.31510596439568</v>
+        <v>40.066082464396</v>
       </c>
       <c r="D15" t="n">
-        <v>1.377112367196669</v>
+        <v>1.632759061134706</v>
       </c>
       <c r="E15" t="n">
-        <v>11.94802163629145</v>
+        <v>11.17119783758128</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756424410053405</v>
+        <v>0.7494288213580005</v>
       </c>
       <c r="G15" t="n">
-        <v>23.27413027551215</v>
+        <v>26.53487008309982</v>
       </c>
       <c r="H15" t="n">
-        <v>36.81757192859385</v>
+        <v>36.18638081198782</v>
       </c>
       <c r="I15" t="n">
-        <v>2.661128622985412</v>
+        <v>1.366813347300604</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72765256283378</v>
+        <v>4.683930133487505</v>
       </c>
       <c r="K15" t="n">
-        <v>18.43795819653328</v>
+        <v>17.67461990405026</v>
       </c>
       <c r="L15" t="n">
-        <v>44.15832791879934</v>
+        <v>42.21376238672189</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91139207972832</v>
+        <v>99.95446475516815</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.81672179321909</v>
+        <v>80.08668117100166</v>
       </c>
       <c r="C16" t="n">
-        <v>34.97996987644293</v>
+        <v>38.0393920653508</v>
       </c>
       <c r="D16" t="n">
-        <v>1.275010623186416</v>
+        <v>1.540572148322371</v>
       </c>
       <c r="E16" t="n">
-        <v>11.43212062977518</v>
+        <v>10.73038809115773</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571345076429269</v>
+        <v>0.7497842748142599</v>
       </c>
       <c r="G16" t="n">
-        <v>21.54854175560872</v>
+        <v>25.03668960254724</v>
       </c>
       <c r="H16" t="n">
-        <v>36.85213462743206</v>
+        <v>36.20354398180805</v>
       </c>
       <c r="I16" t="n">
-        <v>2.219688976805482</v>
+        <v>1.139551354762886</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732090672768293</v>
+        <v>4.686151717589127</v>
       </c>
       <c r="K16" t="n">
-        <v>21.18327820678089</v>
+        <v>19.91331882899835</v>
       </c>
       <c r="L16" t="n">
-        <v>43.76283167724881</v>
+        <v>42.00932206822583</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92607976047265</v>
+        <v>99.96203296257497</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.82385588716649</v>
+        <v>84.54436552699656</v>
       </c>
       <c r="C17" t="n">
-        <v>36.4127471028794</v>
+        <v>40.95684781210249</v>
       </c>
       <c r="D17" t="n">
-        <v>1.276188989814634</v>
+        <v>1.541370569769217</v>
       </c>
       <c r="E17" t="n">
-        <v>12.33004672421536</v>
+        <v>12.29594795861262</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757834252429875</v>
+        <v>0.7501728602149316</v>
       </c>
       <c r="G17" t="n">
-        <v>22.08232984899107</v>
+        <v>26.39058283975893</v>
       </c>
       <c r="H17" t="n">
-        <v>37.40006632307468</v>
+        <v>37.56322458577169</v>
       </c>
       <c r="I17" t="n">
-        <v>2.240925670954161</v>
+        <v>1.314486336525842</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736464077686719</v>
+        <v>4.688580376343324</v>
       </c>
       <c r="K17" t="n">
-        <v>19.1761441128335</v>
+        <v>15.45563447300345</v>
       </c>
       <c r="L17" t="n">
-        <v>44.33648023373432</v>
+        <v>43.54372420023209</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92537144944723</v>
+        <v>99.95620648533803</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.25439634318062</v>
+        <v>86.13437465636355</v>
       </c>
       <c r="C18" t="n">
-        <v>34.18817994798646</v>
+        <v>41.69636868004118</v>
       </c>
       <c r="D18" t="n">
-        <v>1.185250387295542</v>
+        <v>1.542633602716944</v>
       </c>
       <c r="E18" t="n">
-        <v>11.76292040648174</v>
+        <v>12.9029128893649</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7584375561947307</v>
+        <v>0.7507875683568448</v>
       </c>
       <c r="G18" t="n">
-        <v>20.5087884433999</v>
+        <v>26.53420154122173</v>
       </c>
       <c r="H18" t="n">
-        <v>37.42984011694348</v>
+        <v>37.59400471821046</v>
       </c>
       <c r="I18" t="n">
-        <v>1.868924706648152</v>
+        <v>2.117412034262398</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740234726217067</v>
+        <v>4.692422302230282</v>
       </c>
       <c r="K18" t="n">
-        <v>21.74560365681938</v>
+        <v>13.86562534363645</v>
       </c>
       <c r="L18" t="n">
-        <v>44.00396845988987</v>
+        <v>44.36748336296085</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93775206469572</v>
+        <v>99.92947738663847</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.29869440552747</v>
+        <v>83.60689464421124</v>
       </c>
       <c r="C19" t="n">
-        <v>33.51926773164212</v>
+        <v>39.4971405942668</v>
       </c>
       <c r="D19" t="n">
-        <v>1.152167379044365</v>
+        <v>1.448508658593853</v>
       </c>
       <c r="E19" t="n">
-        <v>11.69433812513944</v>
+        <v>12.40992403760869</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7589472727631161</v>
+        <v>0.7513161152051773</v>
       </c>
       <c r="G19" t="n">
-        <v>19.93634195903909</v>
+        <v>24.9151973700306</v>
       </c>
       <c r="H19" t="n">
-        <v>37.45499526584637</v>
+        <v>37.6204705169896</v>
       </c>
       <c r="I19" t="n">
-        <v>1.558483948925608</v>
+        <v>1.765752225750979</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743420454769476</v>
+        <v>4.69572572003236</v>
       </c>
       <c r="K19" t="n">
-        <v>22.70130559447253</v>
+        <v>16.39310535578873</v>
       </c>
       <c r="L19" t="n">
-        <v>43.72751209870068</v>
+        <v>44.05093704899274</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94808542481533</v>
+        <v>99.94118299904828</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.62592555062371</v>
+        <v>80.98663947400766</v>
       </c>
       <c r="C20" t="n">
-        <v>31.08548198509968</v>
+        <v>37.14993437592234</v>
       </c>
       <c r="D20" t="n">
-        <v>1.05884600632037</v>
+        <v>1.351439421599365</v>
       </c>
       <c r="E20" t="n">
-        <v>10.96372095913342</v>
+        <v>11.8236869865763</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593878009672839</v>
+        <v>0.7517714173465269</v>
       </c>
       <c r="G20" t="n">
-        <v>18.32157067445746</v>
+        <v>23.24554963687606</v>
       </c>
       <c r="H20" t="n">
-        <v>37.47673588261083</v>
+        <v>37.64326875123257</v>
       </c>
       <c r="I20" t="n">
-        <v>1.299490471088826</v>
+        <v>1.472351901961052</v>
       </c>
       <c r="J20" t="n">
-        <v>4.746173756045524</v>
+        <v>4.698571358415795</v>
       </c>
       <c r="K20" t="n">
-        <v>25.3740744493763</v>
+        <v>19.01336052599234</v>
       </c>
       <c r="L20" t="n">
-        <v>43.49715234472052</v>
+        <v>43.78765642514777</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95670877919649</v>
+        <v>99.95095132706246</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.22429114077468</v>
+        <v>78.38476262082754</v>
       </c>
       <c r="C21" t="n">
-        <v>35.11925699526283</v>
+        <v>34.77506392893496</v>
       </c>
       <c r="D21" t="n">
-        <v>1.05970399849226</v>
+        <v>1.255548297030801</v>
       </c>
       <c r="E21" t="n">
-        <v>13.1466396086843</v>
+        <v>11.18933962109085</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7600031395384919</v>
+        <v>0.7521638724158504</v>
       </c>
       <c r="G21" t="n">
-        <v>20.18136768938871</v>
+        <v>21.5961661275091</v>
       </c>
       <c r="H21" t="n">
-        <v>39.35205449530203</v>
+        <v>37.66292005920524</v>
       </c>
       <c r="I21" t="n">
-        <v>1.974502587253312</v>
+        <v>1.22760044097663</v>
       </c>
       <c r="J21" t="n">
-        <v>4.750019622115573</v>
+        <v>4.701024202599067</v>
       </c>
       <c r="K21" t="n">
-        <v>18.77570885922531</v>
+        <v>21.61523737917245</v>
       </c>
       <c r="L21" t="n">
-        <v>46.03927068131314</v>
+        <v>43.56880002794924</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93423653580129</v>
+        <v>99.95910133605665</v>
       </c>
     </row>
   </sheetData>
